--- a/py_publication_n/publications.xlsx
+++ b/py_publication_n/publications.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zahidulislam/zahidul-ece.github.io/py_publication_n/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24D21D6E-A0E4-AC4A-8B62-22B84DDB74E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B17BA0E-38B8-1F4C-8D3F-5EE0A6771241}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="49160" yWindow="10420" windowWidth="27640" windowHeight="16940" xr2:uid="{621E45BB-8892-EE41-AFA4-0EFD3539B274}"/>
+    <workbookView xWindow="8940" yWindow="2660" windowWidth="30200" windowHeight="21680" xr2:uid="{621E45BB-8892-EE41-AFA4-0EFD3539B274}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="43">
   <si>
     <t>Year</t>
   </si>
@@ -109,9 +109,6 @@
 Austin, TX, USA, 2025 (accepted).</t>
   </si>
   <si>
-    <t>P. Christou, M. Z. Islam*, Y. Lin, and J. Xiong, “LLM4DistReconfig: A fine-tuned large language model for power distribution network reconfiguration,” 2025 Annual Conference of the Nations of the Americas Chapter of the ACL (NAACL), Albuquerque, New Mexico, USA, April 29–May 4, 2025 (accepted).</t>
-  </si>
-  <si>
     <t>M. Z. Islam, Y. Lin, V. M. Vokkarane, Y. Yao and F. Ding, “Cyber-Physical Reconfiguration for Disaster Resilience
 of Power Distribution Systems,” 2023 IEEE International Conference on Communications, Control, and Computing
 Technologies for Smart Grids (SmartGridComm), Glasgow, United Kingdom, 2023, pp. 1-6.</t>
@@ -126,54 +123,60 @@
 (URTC), Cambridge, MA, USA, 2022, pp. 1-5.</t>
   </si>
   <si>
+    <t>https://ieeexplore.ieee.org/abstract/document/9635789</t>
+  </si>
+  <si>
+    <t>https://ieeexplore.ieee.org/abstract/document/9376595</t>
+  </si>
+  <si>
+    <t>https://ieeexplore.ieee.org/abstract/document/10333954</t>
+  </si>
+  <si>
+    <t>https://ieeexplore.ieee.org/abstract/document/10279789</t>
+  </si>
+  <si>
+    <t>https://ieeexplore.ieee.org/abstract/document/10002244</t>
+  </si>
+  <si>
+    <t>M. Z. Islam, M. S. Reza, M. M. Hossain and M. Ciobotaru, "Accurate Estimation of Phase Angle for Three-Phase Systems in Presence of Unbalances and Distortions," in IEEE Transactions on Instrumentation and Measurement, vol. 71, pp. 1-12, 2022, 9001712.</t>
+  </si>
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>January</t>
+  </si>
+  <si>
+    <t>February</t>
+  </si>
+  <si>
+    <t>March</t>
+  </si>
+  <si>
+    <t>P. Christou, M. Z. Islam*, Y. Lin, and J. Xiong, “LLM4DistReconfig: A fine-tuned large language model for power distribution network reconfiguration,” 2025 Annual Conference of the Nations of the Americas Chapter of the ACL (NAACL), Albuquerque, New Mexico, USA, April 29–May 4, 2025.</t>
+  </si>
+  <si>
     <t>M. Z. Islam, Y. Lin, W. Zhang, “Smart Meter Scheduling for Data-Driven Granular Customer Voltage Visibility”,
-IEEE Transactions on Smart Grid (under review).</t>
+IEEE Transactions on Smart Grid (accepted).</t>
   </si>
   <si>
     <t>M. Z. Islam, Y. Lin, V. M. Vokkarane, “Disaster-Resilient Cyber-Physical Distribution System Reconfiguration and
 Dynamic Networked Microgrid Formation under Intermittent Generation”, IEEE Transactions on Industry Applications
-(under review).</t>
-  </si>
-  <si>
-    <t>M. Z. Islam, Y. Yao, F. Ding, Y. Lin, “Risk-Aware Measurement Synchronization and Recovery for DSSE with
-Heterogeneous Data Sources”, IEEE Transactions on Instrumentation &amp; Measurement (under review).</t>
+(accepted).</t>
+  </si>
+  <si>
+    <t>M. Z. Islam, S.N. Edib, Y. Yao, F. Ding, Y. Lin, “Risk-Aware Measurement Synchronization and Recovery for DSSE with
+Heterogeneous Data Sources”, IEEE Transactions on Instrumentation &amp; Measurement (accepted).</t>
+  </si>
+  <si>
+    <t>June</t>
+  </si>
+  <si>
+    <t>December</t>
   </si>
   <si>
     <t>W. Zhang, Y. Lin, M. Z. Islam, H. Huang, “Neuro-Physics Hybrid State Estimation of Distribution System with
-Smart Meter Voltage Measurements”, (under review).</t>
-  </si>
-  <si>
-    <t>Manuscripts Under Review</t>
-  </si>
-  <si>
-    <t>https://ieeexplore.ieee.org/abstract/document/9635789</t>
-  </si>
-  <si>
-    <t>https://ieeexplore.ieee.org/abstract/document/9376595</t>
-  </si>
-  <si>
-    <t>https://ieeexplore.ieee.org/abstract/document/10333954</t>
-  </si>
-  <si>
-    <t>https://ieeexplore.ieee.org/abstract/document/10279789</t>
-  </si>
-  <si>
-    <t>https://ieeexplore.ieee.org/abstract/document/10002244</t>
-  </si>
-  <si>
-    <t>M. Z. Islam, M. S. Reza, M. M. Hossain and M. Ciobotaru, "Accurate Estimation of Phase Angle for Three-Phase Systems in Presence of Unbalances and Distortions," in IEEE Transactions on Instrumentation and Measurement, vol. 71, pp. 1-12, 2022, 9001712.</t>
-  </si>
-  <si>
-    <t>Month</t>
-  </si>
-  <si>
-    <t>January</t>
-  </si>
-  <si>
-    <t>February</t>
-  </si>
-  <si>
-    <t>March</t>
+Smart Meter Voltage Measurements”, IEEE Transactions on Smart Grid (accepted).</t>
   </si>
 </sst>
 </file>
@@ -590,12 +593,12 @@
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="85" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
@@ -607,7 +610,7 @@
         <v>2025</v>
       </c>
       <c r="E2" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -624,7 +627,7 @@
         <v>2025</v>
       </c>
       <c r="E3" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="68" x14ac:dyDescent="0.2">
@@ -641,7 +644,7 @@
         <v>2024</v>
       </c>
       <c r="E4" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="51" x14ac:dyDescent="0.2">
@@ -658,7 +661,7 @@
         <v>2024</v>
       </c>
       <c r="E5" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
@@ -675,7 +678,7 @@
         <v>2023</v>
       </c>
       <c r="E6" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="68" x14ac:dyDescent="0.2">
@@ -692,7 +695,7 @@
         <v>2023</v>
       </c>
       <c r="E7" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="68" x14ac:dyDescent="0.2">
@@ -709,7 +712,7 @@
         <v>2023</v>
       </c>
       <c r="E8" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="68" x14ac:dyDescent="0.2">
@@ -720,13 +723,13 @@
         <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D9">
         <v>2021</v>
       </c>
       <c r="E9" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="85" x14ac:dyDescent="0.2">
@@ -740,7 +743,7 @@
         <v>2025</v>
       </c>
       <c r="E10" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="85" x14ac:dyDescent="0.2">
@@ -754,131 +757,131 @@
         <v>2025</v>
       </c>
       <c r="E11" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="102" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B12" t="s">
         <v>3</v>
       </c>
       <c r="C12" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D12">
         <v>2023</v>
       </c>
       <c r="E12" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="68" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B13" t="s">
         <v>3</v>
       </c>
       <c r="C13" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D13">
         <v>2023</v>
       </c>
       <c r="E13" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="85" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B14" t="s">
         <v>3</v>
       </c>
       <c r="C14" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D14">
         <v>2022</v>
       </c>
       <c r="E14" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="D15">
         <v>2025</v>
       </c>
       <c r="E15" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="85" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="D16">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E16" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="68" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="D17">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E17" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" ht="68" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="B18" t="s">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="D18">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E18" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="67" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B19" t="s">
         <v>2</v>
       </c>
       <c r="C19" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D19">
         <v>2022</v>
       </c>
       <c r="E19" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/py_publication_n/publications.xlsx
+++ b/py_publication_n/publications.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zahidulislam/zahidul-ece.github.io/py_publication_n/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B17BA0E-38B8-1F4C-8D3F-5EE0A6771241}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02FF563D-AD79-C049-9F5A-7849730E9EB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8940" yWindow="2660" windowWidth="30200" windowHeight="21680" xr2:uid="{621E45BB-8892-EE41-AFA4-0EFD3539B274}"/>
   </bookViews>

--- a/py_publication_n/publications.xlsx
+++ b/py_publication_n/publications.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zahidulislam/zahidul-ece.github.io/py_publication_n/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02FF563D-AD79-C049-9F5A-7849730E9EB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{763429DA-0D79-BD47-BA41-E977B54F4013}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8940" yWindow="2660" windowWidth="30200" windowHeight="21680" xr2:uid="{621E45BB-8892-EE41-AFA4-0EFD3539B274}"/>
+    <workbookView xWindow="4360" yWindow="660" windowWidth="30200" windowHeight="21680" xr2:uid="{621E45BB-8892-EE41-AFA4-0EFD3539B274}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -156,27 +156,27 @@
     <t>P. Christou, M. Z. Islam*, Y. Lin, and J. Xiong, “LLM4DistReconfig: A fine-tuned large language model for power distribution network reconfiguration,” 2025 Annual Conference of the Nations of the Americas Chapter of the ACL (NAACL), Albuquerque, New Mexico, USA, April 29–May 4, 2025.</t>
   </si>
   <si>
+    <t>June</t>
+  </si>
+  <si>
+    <t>December</t>
+  </si>
+  <si>
+    <t>M. Z. Islam, S.N. Edib, Y. Yao, F. Ding, Y. Lin, “Risk-Aware Measurement Synchronization and Recovery for DSSE with
+Heterogeneous Data Sources”, IEEE Transactions on Instrumentation &amp; Measurement, 2026 (accepted).</t>
+  </si>
+  <si>
+    <t>W. Zhang, Y. Lin, M. Z. Islam, H. Huang, “Neuro-Physics Hybrid State Estimation of Distribution System with
+Smart Meter Voltage Measurements”, IEEE Transactions on Smart Grid, 2026 (accepted).</t>
+  </si>
+  <si>
     <t>M. Z. Islam, Y. Lin, W. Zhang, “Smart Meter Scheduling for Data-Driven Granular Customer Voltage Visibility”,
-IEEE Transactions on Smart Grid (accepted).</t>
+IEEE Transactions on Smart Grid, 2025 (accepted).</t>
   </si>
   <si>
     <t>M. Z. Islam, Y. Lin, V. M. Vokkarane, “Disaster-Resilient Cyber-Physical Distribution System Reconfiguration and
-Dynamic Networked Microgrid Formation under Intermittent Generation”, IEEE Transactions on Industry Applications
+Dynamic Networked Microgrid Formation under Intermittent Generation”, IEEE Transactions on Industry Applications, 2025
 (accepted).</t>
-  </si>
-  <si>
-    <t>M. Z. Islam, S.N. Edib, Y. Yao, F. Ding, Y. Lin, “Risk-Aware Measurement Synchronization and Recovery for DSSE with
-Heterogeneous Data Sources”, IEEE Transactions on Instrumentation &amp; Measurement (accepted).</t>
-  </si>
-  <si>
-    <t>June</t>
-  </si>
-  <si>
-    <t>December</t>
-  </si>
-  <si>
-    <t>W. Zhang, Y. Lin, M. Z. Islam, H. Huang, “Neuro-Physics Hybrid State Estimation of Distribution System with
-Smart Meter Voltage Measurements”, IEEE Transactions on Smart Grid (accepted).</t>
   </si>
 </sst>
 </file>
@@ -813,7 +813,7 @@
     </row>
     <row r="15" spans="1:5" ht="51" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B15" t="s">
         <v>2</v>
@@ -822,12 +822,12 @@
         <v>2025</v>
       </c>
       <c r="E15" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="85" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B16" t="s">
         <v>2</v>
@@ -850,12 +850,12 @@
         <v>2026</v>
       </c>
       <c r="E17" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="68" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B18" t="s">
         <v>2</v>

--- a/py_publication_n/publications.xlsx
+++ b/py_publication_n/publications.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zahidulislam/zahidul-ece.github.io/py_publication_n/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{763429DA-0D79-BD47-BA41-E977B54F4013}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0636EDA6-FF9C-1E45-92B1-AF0A1BB05D11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4360" yWindow="660" windowWidth="30200" windowHeight="21680" xr2:uid="{621E45BB-8892-EE41-AFA4-0EFD3539B274}"/>
   </bookViews>
@@ -833,10 +833,10 @@
         <v>2</v>
       </c>
       <c r="D16">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E16" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="68" x14ac:dyDescent="0.2">
